--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_428_Latvia.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_428_Latvia.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rff7ed487c24249e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rd6fa3f342bb54739"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rfeef7def92a846b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R5e7d7ead59fd4749"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rd7885fcf647a488d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rb4f3b4419a954acc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rb40a41a777af4e98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R26a318d3000a4f33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R657bb10e6b874764"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R487cab9129214582"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rb053dc4201544ef0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Ra8858895373a4515"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ428CommercialTable" displayName="EEZ428CommercialTable" ref="A1:O8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O8"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ428CommercialTable" displayName="EEZ428CommercialTable" ref="A1:E8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E8"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ428FunctionalTable" displayName="EEZ428FunctionalTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ428FunctionalTable" displayName="EEZ428FunctionalTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ428ValidationTable" displayName="EEZ428ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ428ValidationTable" displayName="EEZ428ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -3709,7 +3663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae1a07d29e494743"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad61bc8f098a4ebc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3719,20 +3673,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -3740,444 +3684,155 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2529.4714875142995</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.089705961978996</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1229.436102248035</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2529.4714875142995</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1229.6354860719232</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$46,A2,'Species'!$U$2:$U$46))</x:f>
-        <x:v>3110327.9020547164</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.089705961978996</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1229.436102248035</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>3109823.5663571195</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>504.3356975968927</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0001621750195262</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.00016217501952616462</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1640.3376153379002</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.418002421531801</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>261.8197606680064</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1640.3376153379002</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>289.12107172223267</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$46,A3,'Species'!$U$2:$U$46))</x:f>
-        <x:v>474256.1693327851</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.418002421531801</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>261.8197606680064</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>429472.80186249735</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>44783.367470287776</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1042752120182593</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.10427521201825929</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>92008.5403115636</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.1760878497859717</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>149.99882248458016</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>92008.5403115636</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>164.12264183209217</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$46,A4,'Species'!$U$2:$U$46))</x:f>
-        <x:v>15100684.707048366</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.1760878497859717</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>149.99882248458016</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>13801172.705259565</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1299512.0017888006</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0941595348121078</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.09415953481210784</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>611.7323196758001</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.493403003786971</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>311.4605196026926</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>611.7323196758001</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>603.9595410031828</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$46,A5,'Species'!$U$2:$U$46))</x:f>
-        <x:v>369461.57100820856</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.493403003786971</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>311.4605196026926</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>190530.46614398516</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>178931.1048642234</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.939120700670537</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.9391207006705371</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1183.2473960656</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.8352575198215555</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>684.3173006789326</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1183.2473960656</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1263.2148678737196</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$46,A6,'Species'!$U$2:$U$46))</x:f>
-        <x:v>1494695.7030829298</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.8352575198215555</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>684.3173006789326</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>809716.6641109872</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>684979.0389719426</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.8459490453046339</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.845949045304634</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>2176.1040793622997</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.4698400065677184</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>295.01222058779706</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>2176.1040793622997</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>311.15056770775186</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$46,A7,'Species'!$U$2:$U$46))</x:f>
-        <x:v>677096.0196847343</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.4698400065677184</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>295.01222058779706</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>641977.2966828358</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>35118.7230018985</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.054703995271111</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.05470399527111104</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>210.7019553378</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6900127096822413</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>489.7931530164884</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>210.7019553378</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>489.79702397359824</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$46,A8,'Species'!$U$2:$U$46))</x:f>
-        <x:v>103201.19066987245</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6900127096822413</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>489.7931530164884</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>103200.37505164038</x:v>
       </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0.8156182320672087</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0000079032487204</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.000007903248720356704</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G8">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O8">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R716787c7c19c42d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc704bac8b4564869"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4187,20 +3842,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4208,714 +3853,250 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2539.2936880218995</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.091854521923137</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1235.5334904824929</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2539.2936880218995</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1239.5528624122635</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$46,A2,'Species'!$U$2:$U$46))</x:f>
-        <x:v>3147588.7594929384</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.091854521923137</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1235.5334904824929</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>3137382.39372186</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>10206.365771078505</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0032531468881518</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.003253146888151797</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>28.5492216814</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.8913145211474003</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>778.6002182999013</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>28.5492216814</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>880.2798941657667</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$46,A3,'Species'!$U$2:$U$46))</x:f>
-        <x:v>25131.305840217803</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.8913145211474003</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>778.6002182999013</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>22228.430233430314</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>2902.8756067874892</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1305929198014948</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.1305929198014949</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>4.9750434417000005</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.348339641786088</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2230.178587788462</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>4.9750434417000005</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2268.5126517981544</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$46,A4,'Species'!$U$2:$U$46))</x:f>
-        <x:v>11285.948990741885</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.348339641786088</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2230.178587788462</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>11095.235356996758</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>190.71363374512657</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0171887866826421</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.017188786682642183</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>154.87532369049998</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.9901578887645512</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>977.592562399075</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>154.87532369049998</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1032.9008135227168</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$46,A5,'Species'!$U$2:$U$46))</x:f>
-        <x:v>159970.84783451154</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.9901578887645512</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>977.592562399075</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>151404.96453898202</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>8565.883295529522</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0565759737245872</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.05657597372458732</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>151.9170966835</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.9963920324687283</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>99.17267609259557</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>151.9170966835</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>114.5329654185475</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$46,A6,'Species'!$U$2:$U$46))</x:f>
-        <x:v>17399.515580937445</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.9963920324687283</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>99.17267609259557</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>15066.02502232027</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2333.4905586171753</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1548842880029813</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.1548842880029813</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1018.1982638903</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.951301753000294</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>893.9263787452055</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1018.1982638903</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1390.2021521434717</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$46,A7,'Species'!$U$2:$U$46))</x:f>
-        <x:v>1415501.4177690416</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.951301753000294</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>893.9263787452055</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>910194.2868841111</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>505307.1308849305</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.5551640327415808</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.5551640327415809</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>43670.69008286619</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.387765920014699</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>244.21139251526037</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>43670.69008286619</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>248.23814481245557</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$46,A8,'Species'!$U$2:$U$46))</x:f>
-        <x:v>10840731.088850405</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.387765920014699</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>244.21139251526037</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>10664880.037239123</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>175851.05161128193</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0164887979046415</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.01648879790464155</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>13.733903538</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.31</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>204.17379446695296</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>13.733903538</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>204.17379446695293</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$46,A9,'Species'!$U$2:$U$46))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>2804.10319819657</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.31</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>2804.10319819657</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>28.7205326098</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.2698167711721267</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>186.13016878621772</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>28.7205326098</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>190.38206533964575</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$46,A10,'Species'!$U$2:$U$46))</x:f>
-        <x:v>5467.87431590837</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.2698167711721267</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>186.13016878621772</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>5345.757582292144</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>122.11673361622525</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0228436721524257</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.022843672152425634</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>50720.137661740104</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.01</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>102.32929922807536</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>50720.137661740104</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>102.32929922807536</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$46,A11,'Species'!$U$2:$U$46))</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>5190156.143677377</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.01</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>102.32929922807536</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>5190156.143677377</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>393.68177479770003</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.1100000000000003</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>128.82495516931348</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>393.68177479770003</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$46,A12,'Species'!$U$2:$U$46))</x:f>
-        <x:v>50716.03698928943</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.1100000000000003</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>128.82495516931348</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>50716.036989289474</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>-4.3655745685100555e-11</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>0.9999999999999991</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>-8.607877956694456e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>1635.3625718962</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.415172181824879</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>260.11906353923075</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>1635.3625718962</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>283.09943513335395</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$46,A13,'Species'!$U$2:$U$46))</x:f>
-        <x:v>462970.2203420432</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.415172181824879</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>260.11906353923075</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>425388.9807487475</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>37581.23959329573</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.088345587906737</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.08834558790673701</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35fa152dbfc6437a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b20e47c87c043fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5090,7 +4271,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -5189,7 +4370,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>21329723.262881614</x:v>
+        <x:v>19085893.87546863</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5203,7 +4384,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>21329723.26288161</x:v>
+        <x:v>20586662.395192724</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5217,7 +4398,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>7.450580596923828e-9</x:v>
+        <x:v>-2243829.3874129765</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5231,7 +4412,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>3.725290298461914e-9</x:v>
+        <x:v>-743060.8676888831</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5242,9 +4423,9 @@
         <x:v>EEZ_428</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -5256,47 +4437,19 @@
         <x:v>EEZ_428</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_428</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_428</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86a59e943571439d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82fb612ca8a94ee9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5343,7 +4496,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
